--- a/docentes/Moreno Aroyo Anél - Estadisticos 20221.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20221.xlsx
@@ -549,7 +549,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -558,13 +558,13 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>92.86</v>
+        <v>93.02</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -617,16 +617,19 @@
         <v>40</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>40</v>
       </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -640,16 +643,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -663,16 +669,19 @@
         <v>43</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>43</v>
       </c>
-      <c r="E4">
-        <v>43</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -683,19 +692,22 @@
         <v>12</v>
       </c>
       <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>42</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>42</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>97.67</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -751,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -777,13 +789,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>93.18000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="H3">
         <v>9.1</v>
@@ -803,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>95.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -823,19 +835,19 @@
         <v>12</v>
       </c>
       <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>42</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
       <c r="G5">
-        <v>92.86</v>
+        <v>97.67</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20221.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20221.xlsx
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -789,13 +789,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H3">
         <v>9.1</v>
@@ -815,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,7 +850,7 @@
         <v>97.67</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
